--- a/artfynd/A 35283-2025 artfynd.xlsx
+++ b/artfynd/A 35283-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2782,6 +2782,115 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131672033</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58545</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Djupedalen, Dalsland, Dls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>342125</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6474655</v>
+      </c>
+      <c r="S19" t="n">
+        <v>150</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Vänersborg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Frändefors</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Göran Darefelt</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Göran Darefelt, Marita Darefelt</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35283-2025 artfynd.xlsx
+++ b/artfynd/A 35283-2025 artfynd.xlsx
@@ -2787,7 +2787,7 @@
         <v>131672033</v>
       </c>
       <c r="B19" t="n">
-        <v>58545</v>
+        <v>58546</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35283-2025 artfynd.xlsx
+++ b/artfynd/A 35283-2025 artfynd.xlsx
@@ -2787,7 +2787,7 @@
         <v>131672033</v>
       </c>
       <c r="B19" t="n">
-        <v>58546</v>
+        <v>58549</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35283-2025 artfynd.xlsx
+++ b/artfynd/A 35283-2025 artfynd.xlsx
@@ -2787,7 +2787,7 @@
         <v>131672033</v>
       </c>
       <c r="B19" t="n">
-        <v>58549</v>
+        <v>58551</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35283-2025 artfynd.xlsx
+++ b/artfynd/A 35283-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2891,6 +2891,130 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131994581</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57903</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Djupedalen, Dalsland, Dls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>342125</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6474655</v>
+      </c>
+      <c r="S20" t="n">
+        <v>150</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Vänersborg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Frändefors</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Märkligt med tre mycket aktiva fåglar som trummade och spelade ut alla lätesreportoarer utmed stigen väster om bäcken mellan väg 2050 och Länsmansliden.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Göran Darefelt</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Göran Darefelt, Marita Darefelt</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35283-2025 artfynd.xlsx
+++ b/artfynd/A 35283-2025 artfynd.xlsx
@@ -2787,7 +2787,7 @@
         <v>131672033</v>
       </c>
       <c r="B19" t="n">
-        <v>58551</v>
+        <v>58554</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>131994581</v>
       </c>
       <c r="B20" t="n">
-        <v>57903</v>
+        <v>57904</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 35283-2025 artfynd.xlsx
+++ b/artfynd/A 35283-2025 artfynd.xlsx
@@ -2787,7 +2787,7 @@
         <v>131672033</v>
       </c>
       <c r="B19" t="n">
-        <v>58554</v>
+        <v>58559</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>131994581</v>
       </c>
       <c r="B20" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 35283-2025 artfynd.xlsx
+++ b/artfynd/A 35283-2025 artfynd.xlsx
@@ -2787,7 +2787,7 @@
         <v>131672033</v>
       </c>
       <c r="B19" t="n">
-        <v>58559</v>
+        <v>58561</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>131994581</v>
       </c>
       <c r="B20" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 35283-2025 artfynd.xlsx
+++ b/artfynd/A 35283-2025 artfynd.xlsx
@@ -2896,7 +2896,7 @@
         <v>131994581</v>
       </c>
       <c r="B20" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 35283-2025 artfynd.xlsx
+++ b/artfynd/A 35283-2025 artfynd.xlsx
@@ -2896,7 +2896,7 @@
         <v>131994581</v>
       </c>
       <c r="B20" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 35283-2025 artfynd.xlsx
+++ b/artfynd/A 35283-2025 artfynd.xlsx
@@ -3010,7 +3010,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Göran Darefelt, Marita Darefelt</t>
+          <t>Marita Darefelt, Göran Darefelt</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
